--- a/countrylist.xlsx
+++ b/countrylist.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matpo\Documents\GitHub\Eu4-The-Odd-Empires--BETA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9BA0B59-79C7-41DF-9AA2-59AB54B49F9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ACE9597-EBF5-415F-800C-3E34C8ADBE77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{26DFDEC5-5D8D-4408-AA0F-42D64A13A4F2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{26DFDEC5-5D8D-4408-AA0F-42D64A13A4F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>Normal</t>
   </si>
@@ -204,9 +204,6 @@
   </si>
   <si>
     <t>Aegyptus</t>
-  </si>
-  <si>
-    <t>Yakub</t>
   </si>
 </sst>
 </file>
@@ -753,9 +750,7 @@
       <c r="D6" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>56</v>
-      </c>
+      <c r="E6" s="1"/>
       <c r="F6" s="5"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -903,7 +898,7 @@
       <c r="E20" s="1"/>
       <c r="F20" s="5"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="C21" s="1" t="s">
         <v>52</v>
       </c>
